--- a/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
+++ b/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1178" documentId="8_{DBA5D96A-269F-4860-8C1D-BAFFD9162C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A773A0-E9F9-47A2-9B5D-AB8A11E2920C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-27240" yWindow="7680" windowWidth="27120" windowHeight="13275" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mz for main ion" sheetId="2" r:id="rId1"/>
@@ -1200,6 +1200,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>

--- a/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
+++ b/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1178" documentId="8_{DBA5D96A-269F-4860-8C1D-BAFFD9162C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A773A0-E9F9-47A2-9B5D-AB8A11E2920C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mz for main ion" sheetId="2" r:id="rId1"/>

--- a/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
+++ b/Appendix/Internal Standards - Avanti Splash Lipidomix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofc-my.sharepoint.com/personal/adriana_zardinibuzat_ucalgary_ca/Documents/LipidQuest/MetaboScape LipidQuest/260221/Appendix/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofc-my.sharepoint.com/personal/adriana_zardinibuzat_ucalgary_ca/Documents/LipidQuest/MetaboScape LipidQuest/LipidQuest v3/Appendix/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1178" documentId="8_{DBA5D96A-269F-4860-8C1D-BAFFD9162C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A773A0-E9F9-47A2-9B5D-AB8A11E2920C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mz for main ion" sheetId="2" r:id="rId1"/>
@@ -1200,10 +1200,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
